--- a/sharedata/excel/D-单位表(UnitData).xlsx
+++ b/sharedata/excel/D-单位表(UnitData).xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\策划文档\配置表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ThroneOfAshes_Client\sharedata\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="166">
   <si>
     <t>英雄不用配置</t>
   </si>
@@ -42,13 +42,22 @@
     <t>英雄称号：可选；未配置不显示，小兵留空。</t>
   </si>
   <si>
+    <t>命名规则：类型id+阵营id+三位数id+进化分支id</t>
+  </si>
+  <si>
     <t>1:地面；2:飞行</t>
+  </si>
+  <si>
+    <t>配置格子数量</t>
   </si>
   <si>
     <t>1:近战；
 2:远程</t>
   </si>
   <si>
+    <t>为空表示无限距离</t>
+  </si>
+  <si>
     <t>英雄、小兵均适用
 初始星级仅英雄生效</t>
   </si>
@@ -89,12 +98,21 @@
     <t>单位说明</t>
   </si>
   <si>
+    <t>攻击时间</t>
+  </si>
+  <si>
     <t>移动类型</t>
   </si>
   <si>
+    <t>移动距离</t>
+  </si>
+  <si>
     <t>攻击类型</t>
   </si>
   <si>
+    <t>攻击距离</t>
+  </si>
+  <si>
     <t>所需统率值</t>
   </si>
   <si>
@@ -155,12 +173,21 @@
     <t>desc</t>
   </si>
   <si>
+    <t>attack_during</t>
+  </si>
+  <si>
     <t>move_type</t>
   </si>
   <si>
+    <t>move_distance</t>
+  </si>
+  <si>
     <t>attack_type</t>
   </si>
   <si>
+    <t>attack_distance</t>
+  </si>
+  <si>
     <t>need_bonus</t>
   </si>
   <si>
@@ -206,6 +233,9 @@
     <t>lang</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>string_list</t>
   </si>
   <si>
@@ -242,84 +272,162 @@
     <t/>
   </si>
   <si>
+    <t>盾卫步兵</t>
+  </si>
+  <si>
+    <t>小兵</t>
+  </si>
+  <si>
+    <t>圣堂</t>
+  </si>
+  <si>
+    <t>单位图标_临时小兵_1</t>
+  </si>
+  <si>
+    <t>单位立绘_临时小兵_1</t>
+  </si>
+  <si>
+    <t>$Lang$单位说明_临时小兵_1</t>
+  </si>
+  <si>
+    <t>临时小兵近战普攻</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>灰</t>
+  </si>
+  <si>
+    <t>弓射手</t>
+  </si>
+  <si>
+    <t>临时小兵远程普攻</t>
+  </si>
+  <si>
+    <t>铁甲卫</t>
+  </si>
+  <si>
+    <t>SR</t>
+  </si>
+  <si>
+    <t>绿</t>
+  </si>
+  <si>
+    <t>银翼狮鹫</t>
+  </si>
+  <si>
+    <t>SSR</t>
+  </si>
+  <si>
+    <t>蓝</t>
+  </si>
+  <si>
+    <t>圣光修士</t>
+  </si>
+  <si>
+    <t>SSSR</t>
+  </si>
+  <si>
+    <t>紫</t>
+  </si>
+  <si>
+    <t>铁戟骑士</t>
+  </si>
+  <si>
+    <t>圣翼使徒</t>
+  </si>
+  <si>
+    <t>UR</t>
+  </si>
+  <si>
+    <t>金</t>
+  </si>
+  <si>
+    <t>骸弓兵</t>
+  </si>
+  <si>
+    <t>墓园</t>
+  </si>
+  <si>
+    <t>腐烂行尸</t>
+  </si>
+  <si>
+    <t>噬灵幽魂</t>
+  </si>
+  <si>
+    <t>吸血鬼</t>
+  </si>
+  <si>
+    <t>亡骨巫祭</t>
+  </si>
+  <si>
+    <t>黑骑士</t>
+  </si>
+  <si>
+    <t>骸骨巨龙</t>
+  </si>
+  <si>
+    <t>暗行斥候</t>
+  </si>
+  <si>
+    <t>地牢</t>
+  </si>
+  <si>
+    <t>血祭少女</t>
+  </si>
+  <si>
+    <t>牛斗士</t>
+  </si>
+  <si>
+    <t>幽暗女巫</t>
+  </si>
+  <si>
+    <t>蜥蜴掠骑</t>
+  </si>
+  <si>
+    <t>多头蛇蜥</t>
+  </si>
+  <si>
+    <t>暗影龙</t>
+  </si>
+  <si>
+    <t>藤牌兵</t>
+  </si>
+  <si>
+    <t>神机</t>
+  </si>
+  <si>
+    <t>鸟铳手</t>
+  </si>
+  <si>
+    <t>狼筅卫</t>
+  </si>
+  <si>
+    <t>神火飞鸦</t>
+  </si>
+  <si>
+    <t>火炮尉</t>
+  </si>
+  <si>
+    <t>连环铳骑</t>
+  </si>
+  <si>
+    <t>鎏金炎龙</t>
+  </si>
+  <si>
     <t>临时小兵_1</t>
   </si>
   <si>
-    <t>$Lang$临时小兵_1</t>
-  </si>
-  <si>
-    <t>小兵</t>
-  </si>
-  <si>
-    <t>圣堂</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>灰</t>
-  </si>
-  <si>
     <t>临时小兵_2</t>
   </si>
   <si>
-    <t>$Lang$临时小兵_2</t>
-  </si>
-  <si>
-    <t>墓园</t>
-  </si>
-  <si>
     <t>临时小兵_3</t>
   </si>
   <si>
-    <t>$Lang$临时小兵_3</t>
-  </si>
-  <si>
-    <t>地牢</t>
-  </si>
-  <si>
     <t>临时小兵_4</t>
   </si>
   <si>
-    <t>$Lang$临时小兵_4</t>
-  </si>
-  <si>
-    <t>神机</t>
-  </si>
-  <si>
-    <t>临时小兵_5</t>
-  </si>
-  <si>
-    <t>$Lang$临时小兵_5</t>
-  </si>
-  <si>
-    <t>SR</t>
-  </si>
-  <si>
-    <t>绿</t>
-  </si>
-  <si>
-    <t>临时小兵_6</t>
-  </si>
-  <si>
-    <t>$Lang$临时小兵_6</t>
-  </si>
-  <si>
-    <t>临时小兵_7</t>
-  </si>
-  <si>
-    <t>$Lang$临时小兵_7</t>
-  </si>
-  <si>
-    <t>临时小兵_8</t>
-  </si>
-  <si>
-    <t>$Lang$临时小兵_8</t>
-  </si>
-  <si>
-    <t>示例</t>
-  </si>
-  <si>
     <t>临时英雄_1</t>
   </si>
   <si>
@@ -329,34 +437,67 @@
     <t>英雄</t>
   </si>
   <si>
+    <t>单位图标_临时英雄_1</t>
+  </si>
+  <si>
+    <t>单位立绘_临时英雄_1</t>
+  </si>
+  <si>
+    <t>$Lang$临时英雄_1_说明</t>
+  </si>
+  <si>
+    <t>临时英雄普攻</t>
+  </si>
+  <si>
     <t>临时英雄_1_技能1</t>
   </si>
   <si>
     <t>临时英雄_1_技能2</t>
   </si>
   <si>
-    <t>SSSR</t>
-  </si>
-  <si>
-    <t>紫</t>
-  </si>
-  <si>
     <t>临时英雄_2</t>
   </si>
   <si>
     <t>$Lang$临时英雄_2</t>
   </si>
   <si>
+    <t>单位图标_临时英雄_2</t>
+  </si>
+  <si>
+    <t>单位立绘_临时英雄_2</t>
+  </si>
+  <si>
+    <t>$Lang$临时英雄_2_说明</t>
+  </si>
+  <si>
     <t>临时英雄_3</t>
   </si>
   <si>
     <t>$Lang$临时英雄_3</t>
   </si>
   <si>
+    <t>单位图标_临时英雄_3</t>
+  </si>
+  <si>
+    <t>单位立绘_临时英雄_3</t>
+  </si>
+  <si>
+    <t>$Lang$临时英雄_3_说明</t>
+  </si>
+  <si>
     <t>临时英雄_4</t>
   </si>
   <si>
     <t>$Lang$临时英雄_4</t>
+  </si>
+  <si>
+    <t>单位图标_临时英雄_4</t>
+  </si>
+  <si>
+    <t>单位立绘_临时英雄_4</t>
+  </si>
+  <si>
+    <t>$Lang$临时英雄_4_说明</t>
   </si>
   <si>
     <t>单位类型表</t>
@@ -405,7 +546,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
@@ -433,6 +574,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1" tint="0.35"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -447,7 +595,21 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF7030A0"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -573,13 +735,6 @@
       <color theme="0"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-      <b/>
-      <color rgb="FFFF0000"/>
     </font>
   </fonts>
   <fills count="35">
@@ -929,31 +1084,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -962,120 +1105,132 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1097,35 +1252,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1598,32 +1765,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:Y42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="8.22222222222222" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.88888888888889" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.55555555555556" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.66666666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.4444444444444" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5555555555556" style="1" customWidth="1"/>
-    <col min="7" max="8" width="11.8888888888889" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.88888888888889" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.3333333333333" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.4444444444444" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.2222222222222" style="1" customWidth="1"/>
-    <col min="13" max="15" width="18" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.88888888888889" style="1" customWidth="1"/>
-    <col min="17" max="17" width="15.5555555555556" style="1" customWidth="1"/>
-    <col min="18" max="18" width="14.3333333333333" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12" style="1" customWidth="1"/>
-    <col min="20" max="20" width="21.5555555555556" customWidth="1"/>
-    <col min="21" max="21" width="18.6666666666667" customWidth="1"/>
-    <col min="22" max="22" width="20.5555555555556" customWidth="1"/>
-    <col min="23" max="27" width="9" style="1" customWidth="1"/>
+    <col min="7" max="8" width="17.8888888888889" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.6666666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.4444444444444" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7777777777778" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.6666666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.7777777777778" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.2222222222222" style="1" customWidth="1"/>
+    <col min="16" max="18" width="18" style="1" customWidth="1"/>
+    <col min="19" max="19" width="8.88888888888889" style="1" customWidth="1"/>
+    <col min="20" max="20" width="31.5555555555556" style="1" customWidth="1"/>
+    <col min="21" max="21" width="14.3333333333333" style="1" customWidth="1"/>
+    <col min="22" max="22" width="37" style="1" customWidth="1"/>
+    <col min="23" max="23" width="21.5555555555556" customWidth="1"/>
+    <col min="24" max="24" width="18.6666666666667" customWidth="1"/>
+    <col min="25" max="25" width="20.5555555555556" customWidth="1"/>
+    <col min="26" max="30" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:25">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1633,27 +1803,34 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="K1" s="3"/>
       <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
+      <c r="M1" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
-      <c r="Q1"/>
+      <c r="Q1" s="3"/>
       <c r="R1" s="3"/>
-      <c r="S1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="T1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1"/>
       <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-    </row>
-    <row r="2" ht="33" spans="1:22">
+      <c r="V1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -1661,945 +1838,2620 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="J2" s="3"/>
       <c r="K2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
+      <c r="L2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
-      <c r="Q2" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="R2" s="7"/>
-      <c r="T2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="V2" s="3" t="s">
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" s="2" customFormat="1" spans="1:22">
+      <c r="U2" s="8"/>
+      <c r="W2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="X2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y2" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" spans="1:25">
       <c r="A3" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="R3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="S3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="T3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="R3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="V3" s="4" t="s">
+      <c r="S3" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="1:22">
+      <c r="T3" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="U3" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="V3" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" spans="1:25">
       <c r="A4" s="5" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="R4" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="S4" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="T4" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="U4" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="V4" s="5" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="1:22">
+      <c r="Q4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="T4" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="U4" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="V4" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" spans="1:25">
       <c r="A5" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q5" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="R5" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="S5" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="T5" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="U5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="V5" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:22">
+        <v>63</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="T5" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="U5" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="V5" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:25">
       <c r="A6" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
-      <c r="M6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="R6" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="S6" s="9"/>
-      <c r="T6" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="U6" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="V6" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="66.0" customHeight="1">
-      <c r="A7" s="10"/>
-      <c r="B7" s="15">
-        <v>1001</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="G7" s="16" t="str">
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="R6" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="S6" s="5"/>
+      <c r="T6" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="U6" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="V6" s="11"/>
+      <c r="W6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="X6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:25">
+      <c r="A7" s="12"/>
+      <c r="B7" s="13">
+        <v>110010</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="13" t="str">
+        <f>"$Lang$"&amp;C7</f>
+        <v>$Lang$盾卫步兵</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J7" s="13">
+        <v>1</v>
+      </c>
+      <c r="K7" s="13">
+        <v>1</v>
+      </c>
+      <c r="L7" s="13">
+        <v>3</v>
+      </c>
+      <c r="M7" s="13">
+        <v>1</v>
+      </c>
+      <c r="N7" s="13">
+        <v>1</v>
+      </c>
+      <c r="O7" s="13">
+        <v>1</v>
+      </c>
+      <c r="P7" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="U7" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="V7" s="12"/>
+      <c r="W7" s="12"/>
+      <c r="X7" s="12"/>
+      <c r="Y7" s="12"/>
+    </row>
+    <row r="8" customFormat="1" spans="1:25">
+      <c r="A8" s="12"/>
+      <c r="B8" s="13">
+        <v>110020</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="13" t="str">
+        <f t="shared" ref="D8:D38" si="0">"$Lang$"&amp;C8</f>
+        <v>$Lang$弓射手</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="13" t="str">
+        <f t="shared" ref="F8:F13" si="1">F7</f>
+        <v>圣堂</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J8" s="13">
+        <v>1</v>
+      </c>
+      <c r="K8" s="13">
+        <v>1</v>
+      </c>
+      <c r="L8" s="13">
+        <v>3</v>
+      </c>
+      <c r="M8" s="13">
+        <v>2</v>
+      </c>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13">
+        <v>2</v>
+      </c>
+      <c r="P8" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="U8" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="V8" s="12"/>
+      <c r="W8" s="12"/>
+      <c r="X8" s="12"/>
+      <c r="Y8" s="12"/>
+    </row>
+    <row r="9" customFormat="1" spans="1:25">
+      <c r="A9" s="12"/>
+      <c r="B9" s="13">
+        <v>110030</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$铁甲卫</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>圣堂</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J9" s="13">
+        <v>1</v>
+      </c>
+      <c r="K9" s="13">
+        <v>1</v>
+      </c>
+      <c r="L9" s="13">
+        <v>3</v>
+      </c>
+      <c r="M9" s="13">
+        <v>1</v>
+      </c>
+      <c r="N9" s="13">
+        <v>1</v>
+      </c>
+      <c r="O9" s="13">
+        <v>3</v>
+      </c>
+      <c r="P9" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="U9" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="V9" s="12"/>
+      <c r="W9" s="12"/>
+      <c r="X9" s="12"/>
+      <c r="Y9" s="12"/>
+    </row>
+    <row r="10" customFormat="1" spans="1:25">
+      <c r="A10" s="12"/>
+      <c r="B10" s="13">
+        <v>110040</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$银翼狮鹫</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>圣堂</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J10" s="13">
+        <v>1</v>
+      </c>
+      <c r="K10" s="13">
+        <v>2</v>
+      </c>
+      <c r="L10" s="13">
+        <v>3</v>
+      </c>
+      <c r="M10" s="13">
+        <v>1</v>
+      </c>
+      <c r="N10" s="13">
+        <v>1</v>
+      </c>
+      <c r="O10" s="13">
+        <v>4</v>
+      </c>
+      <c r="P10" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="U10" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V10" s="12"/>
+      <c r="W10" s="12"/>
+      <c r="X10" s="12"/>
+      <c r="Y10" s="12"/>
+    </row>
+    <row r="11" customFormat="1" spans="1:25">
+      <c r="A11" s="12"/>
+      <c r="B11" s="13">
+        <v>110050</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$圣光修士</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>圣堂</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J11" s="13">
+        <v>1</v>
+      </c>
+      <c r="K11" s="13">
+        <v>1</v>
+      </c>
+      <c r="L11" s="13">
+        <v>3</v>
+      </c>
+      <c r="M11" s="13">
+        <v>2</v>
+      </c>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13">
+        <v>5</v>
+      </c>
+      <c r="P11" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="U11" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="V11" s="12"/>
+      <c r="W11" s="12"/>
+      <c r="X11" s="12"/>
+      <c r="Y11" s="12"/>
+    </row>
+    <row r="12" customFormat="1" spans="1:25">
+      <c r="A12" s="12"/>
+      <c r="B12" s="13">
+        <v>110060</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$铁戟骑士</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>圣堂</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J12" s="13">
+        <v>1</v>
+      </c>
+      <c r="K12" s="13">
+        <v>1</v>
+      </c>
+      <c r="L12" s="13">
+        <v>3</v>
+      </c>
+      <c r="M12" s="13">
+        <v>1</v>
+      </c>
+      <c r="N12" s="13">
+        <v>1</v>
+      </c>
+      <c r="O12" s="13">
+        <v>6</v>
+      </c>
+      <c r="P12" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="U12" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="V12" s="12"/>
+      <c r="W12" s="12"/>
+      <c r="X12" s="12"/>
+      <c r="Y12" s="12"/>
+    </row>
+    <row r="13" customFormat="1" spans="1:25">
+      <c r="A13" s="12"/>
+      <c r="B13" s="13">
+        <v>110070</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$圣翼使徒</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>圣堂</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J13" s="13">
+        <v>1</v>
+      </c>
+      <c r="K13" s="13">
+        <v>2</v>
+      </c>
+      <c r="L13" s="13">
+        <v>3</v>
+      </c>
+      <c r="M13" s="13">
+        <v>1</v>
+      </c>
+      <c r="N13" s="13">
+        <v>1</v>
+      </c>
+      <c r="O13" s="13">
+        <v>7</v>
+      </c>
+      <c r="P13" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="U13" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="V13" s="12"/>
+      <c r="W13" s="12"/>
+      <c r="X13" s="12"/>
+      <c r="Y13" s="12"/>
+    </row>
+    <row r="14" customFormat="1" spans="1:25">
+      <c r="A14" s="12"/>
+      <c r="B14" s="19">
+        <v>120010</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$骸弓兵</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J14" s="13">
+        <v>1</v>
+      </c>
+      <c r="K14" s="13">
+        <v>1</v>
+      </c>
+      <c r="L14" s="13">
+        <v>3</v>
+      </c>
+      <c r="M14" s="13">
+        <v>2</v>
+      </c>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13">
+        <v>1</v>
+      </c>
+      <c r="P14" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="U14" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="V14" s="12"/>
+      <c r="W14" s="12"/>
+      <c r="X14" s="12"/>
+      <c r="Y14" s="12"/>
+    </row>
+    <row r="15" customFormat="1" spans="1:25">
+      <c r="A15" s="12"/>
+      <c r="B15" s="19">
+        <v>120020</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$腐烂行尸</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="13" t="str">
+        <f t="shared" ref="F15:F20" si="2">F14</f>
+        <v>墓园</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J15" s="13">
+        <v>1</v>
+      </c>
+      <c r="K15" s="13">
+        <v>1</v>
+      </c>
+      <c r="L15" s="13">
+        <v>3</v>
+      </c>
+      <c r="M15" s="13">
+        <v>1</v>
+      </c>
+      <c r="N15" s="13">
+        <v>1</v>
+      </c>
+      <c r="O15" s="13">
+        <v>2</v>
+      </c>
+      <c r="P15" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="U15" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="V15" s="12"/>
+      <c r="W15" s="12"/>
+      <c r="X15" s="12"/>
+      <c r="Y15" s="12"/>
+    </row>
+    <row r="16" customFormat="1" spans="1:25">
+      <c r="A16" s="12"/>
+      <c r="B16" s="19">
+        <v>120030</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$噬灵幽魂</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>墓园</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J16" s="13">
+        <v>1</v>
+      </c>
+      <c r="K16" s="13">
+        <v>1</v>
+      </c>
+      <c r="L16" s="13">
+        <v>3</v>
+      </c>
+      <c r="M16" s="13">
+        <v>1</v>
+      </c>
+      <c r="N16" s="13">
+        <v>1</v>
+      </c>
+      <c r="O16" s="13">
+        <v>3</v>
+      </c>
+      <c r="P16" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="U16" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="V16" s="12"/>
+      <c r="W16" s="12"/>
+      <c r="X16" s="12"/>
+      <c r="Y16" s="12"/>
+    </row>
+    <row r="17" customFormat="1" spans="1:25">
+      <c r="A17" s="12"/>
+      <c r="B17" s="19">
+        <v>120040</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$吸血鬼</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>墓园</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J17" s="13">
+        <v>1</v>
+      </c>
+      <c r="K17" s="13">
+        <v>1</v>
+      </c>
+      <c r="L17" s="13">
+        <v>3</v>
+      </c>
+      <c r="M17" s="13">
+        <v>1</v>
+      </c>
+      <c r="N17" s="13">
+        <v>1</v>
+      </c>
+      <c r="O17" s="13">
+        <v>4</v>
+      </c>
+      <c r="P17" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q17" s="12"/>
+      <c r="R17" s="12"/>
+      <c r="S17" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="U17" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V17" s="12"/>
+      <c r="W17" s="12"/>
+      <c r="X17" s="12"/>
+      <c r="Y17" s="12"/>
+    </row>
+    <row r="18" customFormat="1" spans="1:25">
+      <c r="A18" s="12"/>
+      <c r="B18" s="19">
+        <v>120050</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$亡骨巫祭</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>墓园</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J18" s="13">
+        <v>1</v>
+      </c>
+      <c r="K18" s="13">
+        <v>2</v>
+      </c>
+      <c r="L18" s="13">
+        <v>3</v>
+      </c>
+      <c r="M18" s="13">
+        <v>2</v>
+      </c>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13">
+        <v>5</v>
+      </c>
+      <c r="P18" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="U18" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="V18" s="12"/>
+      <c r="W18" s="12"/>
+      <c r="X18" s="12"/>
+      <c r="Y18" s="12"/>
+    </row>
+    <row r="19" customFormat="1" spans="1:25">
+      <c r="A19" s="12"/>
+      <c r="B19" s="19">
+        <v>120060</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$黑骑士</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>墓园</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J19" s="13">
+        <v>1</v>
+      </c>
+      <c r="K19" s="13">
+        <v>1</v>
+      </c>
+      <c r="L19" s="13">
+        <v>3</v>
+      </c>
+      <c r="M19" s="13">
+        <v>1</v>
+      </c>
+      <c r="N19" s="13">
+        <v>1</v>
+      </c>
+      <c r="O19" s="13">
+        <v>6</v>
+      </c>
+      <c r="P19" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q19" s="12"/>
+      <c r="R19" s="12"/>
+      <c r="S19" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="U19" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="V19" s="12"/>
+      <c r="W19" s="12"/>
+      <c r="X19" s="12"/>
+      <c r="Y19" s="12"/>
+    </row>
+    <row r="20" customFormat="1" spans="1:25">
+      <c r="A20" s="12"/>
+      <c r="B20" s="19">
+        <v>120070</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$骸骨巨龙</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>墓园</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J20" s="13">
+        <v>1</v>
+      </c>
+      <c r="K20" s="13">
+        <v>2</v>
+      </c>
+      <c r="L20" s="13">
+        <v>3</v>
+      </c>
+      <c r="M20" s="13">
+        <v>1</v>
+      </c>
+      <c r="N20" s="13">
+        <v>1</v>
+      </c>
+      <c r="O20" s="13">
+        <v>7</v>
+      </c>
+      <c r="P20" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="12"/>
+      <c r="S20" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="U20" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="V20" s="12"/>
+      <c r="W20" s="12"/>
+      <c r="X20" s="12"/>
+      <c r="Y20" s="12"/>
+    </row>
+    <row r="21" customFormat="1" spans="1:25">
+      <c r="A21" s="12"/>
+      <c r="B21" s="19">
+        <v>130010</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$暗行斥候</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J21" s="13">
+        <v>1</v>
+      </c>
+      <c r="K21" s="13">
+        <v>1</v>
+      </c>
+      <c r="L21" s="13">
+        <v>3</v>
+      </c>
+      <c r="M21" s="13">
+        <v>2</v>
+      </c>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13">
+        <v>1</v>
+      </c>
+      <c r="P21" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q21" s="12"/>
+      <c r="R21" s="12"/>
+      <c r="S21" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="U21" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="V21" s="12"/>
+      <c r="W21" s="12"/>
+      <c r="X21" s="12"/>
+      <c r="Y21" s="12"/>
+    </row>
+    <row r="22" customFormat="1" spans="1:25">
+      <c r="A22" s="12"/>
+      <c r="B22" s="19">
+        <v>130020</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D22" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$血祭少女</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" s="13" t="str">
+        <f t="shared" ref="F22:F27" si="3">F21</f>
+        <v>地牢</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J22" s="13">
+        <v>1</v>
+      </c>
+      <c r="K22" s="13">
+        <v>1</v>
+      </c>
+      <c r="L22" s="13">
+        <v>3</v>
+      </c>
+      <c r="M22" s="13">
+        <v>1</v>
+      </c>
+      <c r="N22" s="13">
+        <v>1</v>
+      </c>
+      <c r="O22" s="13">
+        <v>2</v>
+      </c>
+      <c r="P22" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q22" s="12"/>
+      <c r="R22" s="12"/>
+      <c r="S22" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="U22" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="V22" s="12"/>
+      <c r="W22" s="12"/>
+      <c r="X22" s="12"/>
+      <c r="Y22" s="12"/>
+    </row>
+    <row r="23" customFormat="1" spans="1:25">
+      <c r="A23" s="12"/>
+      <c r="B23" s="19">
+        <v>130030</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D23" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$牛斗士</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F23" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>地牢</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J23" s="13">
+        <v>1</v>
+      </c>
+      <c r="K23" s="13">
+        <v>1</v>
+      </c>
+      <c r="L23" s="13">
+        <v>3</v>
+      </c>
+      <c r="M23" s="13">
+        <v>1</v>
+      </c>
+      <c r="N23" s="13">
+        <v>1</v>
+      </c>
+      <c r="O23" s="13">
+        <v>3</v>
+      </c>
+      <c r="P23" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q23" s="12"/>
+      <c r="R23" s="12"/>
+      <c r="S23" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="U23" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="V23" s="12"/>
+      <c r="W23" s="12"/>
+      <c r="X23" s="12"/>
+      <c r="Y23" s="12"/>
+    </row>
+    <row r="24" customFormat="1" spans="1:25">
+      <c r="A24" s="12"/>
+      <c r="B24" s="19">
+        <v>130040</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$幽暗女巫</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F24" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>地牢</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J24" s="13">
+        <v>1</v>
+      </c>
+      <c r="K24" s="13">
+        <v>2</v>
+      </c>
+      <c r="L24" s="13">
+        <v>3</v>
+      </c>
+      <c r="M24" s="13">
+        <v>2</v>
+      </c>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13">
+        <v>4</v>
+      </c>
+      <c r="P24" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q24" s="12"/>
+      <c r="R24" s="12"/>
+      <c r="S24" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="U24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V24" s="12"/>
+      <c r="W24" s="12"/>
+      <c r="X24" s="12"/>
+      <c r="Y24" s="12"/>
+    </row>
+    <row r="25" customFormat="1" spans="1:25">
+      <c r="A25" s="12"/>
+      <c r="B25" s="19">
+        <v>130050</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$蜥蜴掠骑</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F25" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>地牢</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J25" s="13">
+        <v>1</v>
+      </c>
+      <c r="K25" s="13">
+        <v>1</v>
+      </c>
+      <c r="L25" s="13">
+        <v>3</v>
+      </c>
+      <c r="M25" s="13">
+        <v>1</v>
+      </c>
+      <c r="N25" s="13">
+        <v>1</v>
+      </c>
+      <c r="O25" s="13">
+        <v>5</v>
+      </c>
+      <c r="P25" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q25" s="12"/>
+      <c r="R25" s="12"/>
+      <c r="S25" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="U25" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="V25" s="12"/>
+      <c r="W25" s="12"/>
+      <c r="X25" s="12"/>
+      <c r="Y25" s="12"/>
+    </row>
+    <row r="26" customFormat="1" spans="1:25">
+      <c r="A26" s="12"/>
+      <c r="B26" s="19">
+        <v>130060</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$多头蛇蜥</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>地牢</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J26" s="13">
+        <v>1</v>
+      </c>
+      <c r="K26" s="13">
+        <v>1</v>
+      </c>
+      <c r="L26" s="13">
+        <v>3</v>
+      </c>
+      <c r="M26" s="13">
+        <v>1</v>
+      </c>
+      <c r="N26" s="13">
+        <v>1</v>
+      </c>
+      <c r="O26" s="13">
+        <v>6</v>
+      </c>
+      <c r="P26" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q26" s="12"/>
+      <c r="R26" s="12"/>
+      <c r="S26" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="U26" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="V26" s="12"/>
+      <c r="W26" s="12"/>
+      <c r="X26" s="12"/>
+      <c r="Y26" s="12"/>
+    </row>
+    <row r="27" customFormat="1" spans="1:25">
+      <c r="A27" s="12"/>
+      <c r="B27" s="19">
+        <v>130070</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$暗影龙</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F27" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>地牢</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J27" s="13">
+        <v>1</v>
+      </c>
+      <c r="K27" s="13">
+        <v>2</v>
+      </c>
+      <c r="L27" s="13">
+        <v>3</v>
+      </c>
+      <c r="M27" s="13">
+        <v>1</v>
+      </c>
+      <c r="N27" s="13">
+        <v>1</v>
+      </c>
+      <c r="O27" s="13">
+        <v>7</v>
+      </c>
+      <c r="P27" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q27" s="12"/>
+      <c r="R27" s="12"/>
+      <c r="S27" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="U27" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="V27" s="12"/>
+      <c r="W27" s="12"/>
+      <c r="X27" s="12"/>
+      <c r="Y27" s="12"/>
+    </row>
+    <row r="28" customFormat="1" spans="1:25">
+      <c r="A28" s="12"/>
+      <c r="B28" s="19">
+        <v>140010</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$藤牌兵</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J28" s="13">
+        <v>1</v>
+      </c>
+      <c r="K28" s="13">
+        <v>1</v>
+      </c>
+      <c r="L28" s="13">
+        <v>3</v>
+      </c>
+      <c r="M28" s="13">
+        <v>1</v>
+      </c>
+      <c r="N28" s="13">
+        <v>1</v>
+      </c>
+      <c r="O28" s="13">
+        <v>1</v>
+      </c>
+      <c r="P28" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q28" s="12"/>
+      <c r="R28" s="12"/>
+      <c r="S28" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="U28" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="V28" s="12"/>
+      <c r="W28" s="12"/>
+      <c r="X28" s="12"/>
+      <c r="Y28" s="12"/>
+    </row>
+    <row r="29" customFormat="1" spans="1:25">
+      <c r="A29" s="12"/>
+      <c r="B29" s="19">
+        <v>140020</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D29" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$鸟铳手</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" s="13" t="str">
+        <f t="shared" ref="F29:F34" si="4">F28</f>
+        <v>神机</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J29" s="13">
+        <v>1</v>
+      </c>
+      <c r="K29" s="13">
+        <v>1</v>
+      </c>
+      <c r="L29" s="13">
+        <v>3</v>
+      </c>
+      <c r="M29" s="13">
+        <v>2</v>
+      </c>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13">
+        <v>2</v>
+      </c>
+      <c r="P29" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q29" s="12"/>
+      <c r="R29" s="12"/>
+      <c r="S29" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="U29" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="V29" s="12"/>
+      <c r="W29" s="12"/>
+      <c r="X29" s="12"/>
+      <c r="Y29" s="12"/>
+    </row>
+    <row r="30" customFormat="1" spans="1:25">
+      <c r="A30" s="12"/>
+      <c r="B30" s="19">
+        <v>140030</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$狼筅卫</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F30" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v>神机</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J30" s="13">
+        <v>1</v>
+      </c>
+      <c r="K30" s="13">
+        <v>1</v>
+      </c>
+      <c r="L30" s="13">
+        <v>3</v>
+      </c>
+      <c r="M30" s="13">
+        <v>1</v>
+      </c>
+      <c r="N30" s="13">
+        <v>1</v>
+      </c>
+      <c r="O30" s="13">
+        <v>3</v>
+      </c>
+      <c r="P30" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q30" s="12"/>
+      <c r="R30" s="12"/>
+      <c r="S30" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="U30" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="V30" s="12"/>
+      <c r="W30" s="12"/>
+      <c r="X30" s="12"/>
+      <c r="Y30" s="12"/>
+    </row>
+    <row r="31" customFormat="1" spans="1:25">
+      <c r="A31" s="12"/>
+      <c r="B31" s="19">
+        <v>140040</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$神火飞鸦</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F31" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v>神机</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J31" s="13">
+        <v>1</v>
+      </c>
+      <c r="K31" s="13">
+        <v>2</v>
+      </c>
+      <c r="L31" s="13">
+        <v>3</v>
+      </c>
+      <c r="M31" s="13">
+        <v>2</v>
+      </c>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13">
+        <v>4</v>
+      </c>
+      <c r="P31" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q31" s="12"/>
+      <c r="R31" s="12"/>
+      <c r="S31" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="U31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V31" s="12"/>
+      <c r="W31" s="12"/>
+      <c r="X31" s="12"/>
+      <c r="Y31" s="12"/>
+    </row>
+    <row r="32" customFormat="1" spans="1:25">
+      <c r="A32" s="12"/>
+      <c r="B32" s="19">
+        <v>140050</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D32" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$火炮尉</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F32" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v>神机</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J32" s="13">
+        <v>1</v>
+      </c>
+      <c r="K32" s="13">
+        <v>1</v>
+      </c>
+      <c r="L32" s="13">
+        <v>3</v>
+      </c>
+      <c r="M32" s="13">
+        <v>2</v>
+      </c>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13">
+        <v>5</v>
+      </c>
+      <c r="P32" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q32" s="12"/>
+      <c r="R32" s="12"/>
+      <c r="S32" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="U32" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="V32" s="12"/>
+      <c r="W32" s="12"/>
+      <c r="X32" s="12"/>
+      <c r="Y32" s="12"/>
+    </row>
+    <row r="33" customFormat="1" spans="1:25">
+      <c r="A33" s="12"/>
+      <c r="B33" s="19">
+        <v>140060</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D33" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$连环铳骑</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F33" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v>神机</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J33" s="13">
+        <v>1</v>
+      </c>
+      <c r="K33" s="13">
+        <v>1</v>
+      </c>
+      <c r="L33" s="13">
+        <v>3</v>
+      </c>
+      <c r="M33" s="13">
+        <v>2</v>
+      </c>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13">
+        <v>6</v>
+      </c>
+      <c r="P33" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q33" s="12"/>
+      <c r="R33" s="12"/>
+      <c r="S33" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="U33" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="V33" s="12"/>
+      <c r="W33" s="12"/>
+      <c r="X33" s="12"/>
+      <c r="Y33" s="12"/>
+    </row>
+    <row r="34" customFormat="1" spans="1:25">
+      <c r="A34" s="12"/>
+      <c r="B34" s="19">
+        <v>140070</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$鎏金炎龙</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F34" s="13" t="str">
+        <f t="shared" si="4"/>
+        <v>神机</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J34" s="13">
+        <v>1</v>
+      </c>
+      <c r="K34" s="13">
+        <v>2</v>
+      </c>
+      <c r="L34" s="13">
+        <v>3</v>
+      </c>
+      <c r="M34" s="13">
+        <v>1</v>
+      </c>
+      <c r="N34" s="13">
+        <v>1</v>
+      </c>
+      <c r="O34" s="13">
+        <v>7</v>
+      </c>
+      <c r="P34" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q34" s="12"/>
+      <c r="R34" s="12"/>
+      <c r="S34" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="U34" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="V34" s="12"/>
+      <c r="W34" s="12"/>
+      <c r="X34" s="12"/>
+      <c r="Y34" s="12"/>
+    </row>
+    <row r="35" customFormat="1" spans="1:25">
+      <c r="B35" s="13">
+        <v>11001</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="D35" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$临时小兵_1</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G35" s="13" t="str">
+        <f>"单位图标_"&amp;C35</f>
         <v>单位图标_临时小兵_1</v>
       </c>
-      <c r="H7" s="16" t="str">
+      <c r="H35" s="13" t="str">
+        <f>"单位立绘_"&amp;C35</f>
         <v>单位立绘_临时小兵_1</v>
       </c>
-      <c r="I7" s="16" t="str">
-        <v>$Lang$临时小兵_1_说明</v>
-      </c>
-      <c r="J7" s="15">
-        <v>1</v>
-      </c>
-      <c r="K7" s="15">
-        <v>1</v>
-      </c>
-      <c r="L7" s="15">
-        <v>1</v>
-      </c>
-      <c r="M7" s="16" t="str">
-        <v>临时小兵近战普攻</v>
-      </c>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="15" t="b">
+      <c r="I35" s="13" t="str">
+        <f>"$Lang$单位说明_"&amp;C35</f>
+        <v>$Lang$单位说明_临时小兵_1</v>
+      </c>
+      <c r="J35" s="13">
+        <v>1</v>
+      </c>
+      <c r="K35" s="13">
+        <v>1</v>
+      </c>
+      <c r="L35" s="13">
+        <v>3</v>
+      </c>
+      <c r="M35" s="13">
+        <v>1</v>
+      </c>
+      <c r="N35" s="13">
+        <v>1</v>
+      </c>
+      <c r="O35" s="13">
+        <v>1</v>
+      </c>
+      <c r="P35" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q35" s="13"/>
+      <c r="R35" s="13"/>
+      <c r="S35" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="Q7" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="R7" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10"/>
-      <c r="U7" s="10"/>
-      <c r="V7" s="10"/>
-    </row>
-    <row r="8" spans="1:22" ht="66.0" customHeight="1">
-      <c r="A8" s="10"/>
-      <c r="B8" s="15">
-        <v>1002</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="G8" s="16" t="str">
+      <c r="T35" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="U35" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="V35" s="12"/>
+      <c r="W35" s="20"/>
+      <c r="X35" s="13"/>
+      <c r="Y35" s="13"/>
+    </row>
+    <row r="36" customFormat="1" spans="1:25">
+      <c r="B36" s="13">
+        <v>11002</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D36" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$临时小兵_2</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="G36" s="13" t="str">
+        <f>"单位图标_"&amp;C36</f>
         <v>单位图标_临时小兵_2</v>
       </c>
-      <c r="H8" s="16" t="str">
+      <c r="H36" s="13" t="str">
+        <f>"单位立绘_"&amp;C36</f>
         <v>单位立绘_临时小兵_2</v>
       </c>
-      <c r="I8" s="16" t="str">
-        <v>$Lang$临时小兵_2_说明</v>
-      </c>
-      <c r="J8" s="15">
-        <v>1</v>
-      </c>
-      <c r="K8" s="15">
-        <v>1</v>
-      </c>
-      <c r="L8" s="15">
-        <v>1</v>
-      </c>
-      <c r="M8" s="16" t="str">
-        <v>临时小兵近战普攻</v>
-      </c>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="15" t="b">
+      <c r="I36" s="13" t="str">
+        <f>"$Lang$单位说明_"&amp;C36</f>
+        <v>$Lang$单位说明_临时小兵_2</v>
+      </c>
+      <c r="J36" s="13">
+        <v>1</v>
+      </c>
+      <c r="K36" s="13">
+        <v>1</v>
+      </c>
+      <c r="L36" s="13">
+        <v>3</v>
+      </c>
+      <c r="M36" s="13">
+        <v>1</v>
+      </c>
+      <c r="N36" s="13">
+        <v>1</v>
+      </c>
+      <c r="O36" s="13">
+        <v>1</v>
+      </c>
+      <c r="P36" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q36" s="13"/>
+      <c r="R36" s="13"/>
+      <c r="S36" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="Q8" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="R8" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="S8" s="10"/>
-      <c r="T8" s="10"/>
-      <c r="U8" s="10"/>
-      <c r="V8" s="10"/>
-    </row>
-    <row r="9" spans="1:22" ht="66.0" customHeight="1">
-      <c r="A9" s="10"/>
-      <c r="B9" s="15">
-        <v>1003</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="F9" s="15" t="s">
+      <c r="T36" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="U36" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="V36" s="12"/>
+      <c r="W36" s="20"/>
+      <c r="X36" s="13"/>
+      <c r="Y36" s="13"/>
+    </row>
+    <row r="37" customFormat="1" spans="1:25">
+      <c r="B37" s="13">
+        <v>11003</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="D37" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$临时小兵_3</v>
+      </c>
+      <c r="E37" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="G9" s="16" t="str">
+      <c r="F37" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G37" s="13" t="str">
+        <f>"单位图标_"&amp;C37</f>
         <v>单位图标_临时小兵_3</v>
       </c>
-      <c r="H9" s="16" t="str">
+      <c r="H37" s="13" t="str">
+        <f>"单位立绘_"&amp;C37</f>
         <v>单位立绘_临时小兵_3</v>
       </c>
-      <c r="I9" s="16" t="str">
-        <v>$Lang$临时小兵_3_说明</v>
-      </c>
-      <c r="J9" s="15">
-        <v>1</v>
-      </c>
-      <c r="K9" s="15">
-        <v>1</v>
-      </c>
-      <c r="L9" s="15">
-        <v>1</v>
-      </c>
-      <c r="M9" s="16" t="str">
-        <v>临时小兵近战普攻</v>
-      </c>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="15" t="b">
+      <c r="I37" s="13" t="str">
+        <f>"$Lang$单位说明_"&amp;C37</f>
+        <v>$Lang$单位说明_临时小兵_3</v>
+      </c>
+      <c r="J37" s="13">
+        <v>1</v>
+      </c>
+      <c r="K37" s="13">
+        <v>1</v>
+      </c>
+      <c r="L37" s="13">
+        <v>3</v>
+      </c>
+      <c r="M37" s="13">
+        <v>1</v>
+      </c>
+      <c r="N37" s="13">
+        <v>1</v>
+      </c>
+      <c r="O37" s="13">
+        <v>1</v>
+      </c>
+      <c r="P37" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q37" s="13"/>
+      <c r="R37" s="13"/>
+      <c r="S37" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="Q9" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="R9" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="S9" s="10"/>
-      <c r="T9" s="10"/>
-      <c r="U9" s="10"/>
-      <c r="V9" s="10"/>
-    </row>
-    <row r="10" spans="1:22" ht="66.0" customHeight="1">
-      <c r="A10" s="10"/>
-      <c r="B10" s="15">
-        <v>1004</v>
-      </c>
-      <c r="C10" s="16" t="s">
+      <c r="T37" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="U37" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="V37" s="12"/>
+      <c r="W37" s="20"/>
+      <c r="X37" s="13"/>
+      <c r="Y37" s="13"/>
+    </row>
+    <row r="38" customFormat="1" spans="1:25">
+      <c r="B38" s="13">
+        <v>11004</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="D38" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>$Lang$临时小兵_4</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="G38" s="13" t="str">
+        <f>"单位图标_"&amp;C38</f>
+        <v>单位图标_临时小兵_4</v>
+      </c>
+      <c r="H38" s="13" t="str">
+        <f>"单位立绘_"&amp;C38</f>
+        <v>单位立绘_临时小兵_4</v>
+      </c>
+      <c r="I38" s="13" t="str">
+        <f>"$Lang$单位说明_"&amp;C38</f>
+        <v>$Lang$单位说明_临时小兵_4</v>
+      </c>
+      <c r="J38" s="13">
+        <v>1</v>
+      </c>
+      <c r="K38" s="13">
+        <v>1</v>
+      </c>
+      <c r="L38" s="13">
+        <v>3</v>
+      </c>
+      <c r="M38" s="13">
+        <v>1</v>
+      </c>
+      <c r="N38" s="13">
+        <v>1</v>
+      </c>
+      <c r="O38" s="13">
+        <v>1</v>
+      </c>
+      <c r="P38" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q38" s="13"/>
+      <c r="R38" s="13"/>
+      <c r="S38" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="U38" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="V38" s="12"/>
+      <c r="W38" s="20"/>
+      <c r="X38" s="13"/>
+      <c r="Y38" s="13"/>
+    </row>
+    <row r="39" spans="1:25">
+      <c r="A39"/>
+      <c r="B39" s="13">
+        <v>21001</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F39" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D10" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="G10" s="16" t="str">
-        <v>单位图标_临时小兵_4</v>
-      </c>
-      <c r="H10" s="16" t="str">
-        <v>单位立绘_临时小兵_4</v>
-      </c>
-      <c r="I10" s="16" t="str">
-        <v>$Lang$临时小兵_4_说明</v>
-      </c>
-      <c r="J10" s="15">
-        <v>1</v>
-      </c>
-      <c r="K10" s="15">
-        <v>1</v>
-      </c>
-      <c r="L10" s="15">
-        <v>1</v>
-      </c>
-      <c r="M10" s="16" t="str">
-        <v>临时小兵近战普攻</v>
-      </c>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="15" t="b">
+      <c r="G39" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="H39" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="I39" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13">
+        <v>1</v>
+      </c>
+      <c r="L39"/>
+      <c r="M39"/>
+      <c r="N39"/>
+      <c r="O39"/>
+      <c r="P39" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q39" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="R39" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="S39" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="Q10" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="R10" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
-      <c r="U10" s="10"/>
-      <c r="V10" s="10"/>
-    </row>
-    <row r="11" spans="1:22" ht="66.0" customHeight="1">
-      <c r="A11" s="10"/>
-      <c r="B11" s="15">
-        <v>1005</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="16" t="str">
-        <v>单位图标_临时小兵_5</v>
-      </c>
-      <c r="H11" s="16" t="str">
-        <v>单位立绘_临时小兵_5</v>
-      </c>
-      <c r="I11" s="16" t="str">
-        <v>$Lang$临时小兵_5_说明</v>
-      </c>
-      <c r="J11" s="15">
-        <v>2</v>
-      </c>
-      <c r="K11" s="15">
-        <v>2</v>
-      </c>
-      <c r="L11" s="15">
-        <v>2</v>
-      </c>
-      <c r="M11" s="16" t="str">
-        <v>临时小兵远程普攻</v>
-      </c>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="15" t="b">
+      <c r="T39" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="U39" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="V39" s="12"/>
+      <c r="W39" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="X39" s="13">
+        <v>4</v>
+      </c>
+      <c r="Y39" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25">
+      <c r="B40" s="13">
+        <v>21002</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13">
+        <v>1</v>
+      </c>
+      <c r="L40"/>
+      <c r="M40"/>
+      <c r="N40"/>
+      <c r="O40"/>
+      <c r="P40" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q40" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="R40" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="S40" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="Q11" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="R11" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
-      <c r="U11" s="10"/>
-      <c r="V11" s="10"/>
-    </row>
-    <row r="12" spans="1:22" ht="66.0" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="15">
-        <v>1006</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12" s="16" t="str">
-        <v>单位图标_临时小兵_6</v>
-      </c>
-      <c r="H12" s="16" t="str">
-        <v>单位立绘_临时小兵_6</v>
-      </c>
-      <c r="I12" s="16" t="str">
-        <v>$Lang$临时小兵_6_说明</v>
-      </c>
-      <c r="J12" s="15">
-        <v>2</v>
-      </c>
-      <c r="K12" s="15">
-        <v>2</v>
-      </c>
-      <c r="L12" s="15">
-        <v>2</v>
-      </c>
-      <c r="M12" s="16" t="str">
-        <v>临时小兵远程普攻</v>
-      </c>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="15" t="b">
+      <c r="T40" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="U40" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="V40" s="12"/>
+      <c r="W40" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="X40" s="13">
+        <v>4</v>
+      </c>
+      <c r="Y40" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25">
+      <c r="B41" s="13">
+        <v>21003</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="I41" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13">
+        <v>1</v>
+      </c>
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+      <c r="P41" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q41" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="R41" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="S41" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="Q12" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="R12" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10"/>
-      <c r="U12" s="10"/>
-      <c r="V12" s="10"/>
-    </row>
-    <row r="13" spans="1:22" ht="66.0" customHeight="1">
-      <c r="A13" s="10"/>
-      <c r="B13" s="15">
-        <v>1007</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="G13" s="16" t="str">
-        <v>单位图标_临时小兵_7</v>
-      </c>
-      <c r="H13" s="16" t="str">
-        <v>单位立绘_临时小兵_7</v>
-      </c>
-      <c r="I13" s="16" t="str">
-        <v>$Lang$临时小兵_7_说明</v>
-      </c>
-      <c r="J13" s="15">
-        <v>2</v>
-      </c>
-      <c r="K13" s="15">
-        <v>2</v>
-      </c>
-      <c r="L13" s="15">
-        <v>2</v>
-      </c>
-      <c r="M13" s="16" t="str">
-        <v>临时小兵远程普攻</v>
-      </c>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="15" t="b">
+      <c r="T41" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="U41" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="V41" s="12"/>
+      <c r="W41" s="17"/>
+      <c r="X41" s="6"/>
+    </row>
+    <row r="42" spans="1:25">
+      <c r="B42" s="13">
+        <v>21004</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="J42" s="13"/>
+      <c r="K42" s="13">
+        <v>1</v>
+      </c>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
+      <c r="P42" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q42" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="R42" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="S42" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="Q13" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="R13" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="10"/>
-    </row>
-    <row r="14" spans="1:22" ht="66.0" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="15">
-        <v>1008</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="G14" s="16" t="str">
-        <v>单位图标_临时小兵_8</v>
-      </c>
-      <c r="H14" s="16" t="str">
-        <v>单位立绘_临时小兵_8</v>
-      </c>
-      <c r="I14" s="16" t="str">
-        <v>$Lang$临时小兵_8_说明</v>
-      </c>
-      <c r="J14" s="15">
-        <v>2</v>
-      </c>
-      <c r="K14" s="15">
-        <v>2</v>
-      </c>
-      <c r="L14" s="15">
-        <v>2</v>
-      </c>
-      <c r="M14" s="16" t="str">
-        <v>临时小兵远程普攻</v>
-      </c>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="R14" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="S14" s="10"/>
-      <c r="T14" s="10"/>
-      <c r="U14" s="10"/>
-      <c r="V14" s="10"/>
-    </row>
-    <row r="15" spans="1:22" ht="66.0" customHeight="1">
-      <c r="A15" t="s">
-        <v>93</v>
-      </c>
-      <c r="B15" s="15">
-        <v>2001</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" s="15" t="s">
+      <c r="T42" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="F15" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" t="str" s="16">
-        <v>单位图标_临时英雄_1</v>
-      </c>
-      <c r="H15" t="str" s="16">
-        <v>单位立绘_临时英雄_1</v>
-      </c>
-      <c r="I15" t="str" s="16">
-        <v>$Lang$临时英雄_1_说明</v>
-      </c>
-      <c r="J15" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15"/>
-      <c r="L15"/>
-      <c r="M15" s="15" t="str">
-        <v>临时英雄普攻</v>
-      </c>
-      <c r="N15" s="16" t="s">
+      <c r="U42" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="O15" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="P15" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="R15" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="S15" s="10"/>
-      <c r="T15" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="U15" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="V15" t="n" s="15">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="66.0" customHeight="1">
-      <c r="B16" s="15">
-        <v>2002</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="G16" t="str" s="16">
-        <v>单位图标_临时英雄_2</v>
-      </c>
-      <c r="H16" t="str" s="16">
-        <v>单位立绘_临时英雄_2</v>
-      </c>
-      <c r="I16" t="str" s="16">
-        <v>$Lang$临时英雄_2_说明</v>
-      </c>
-      <c r="J16" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16"/>
-      <c r="L16"/>
-      <c r="M16" s="15" t="str">
-        <v>临时英雄普攻</v>
-      </c>
-      <c r="N16" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="O16" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="P16" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="R16" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="S16" s="10"/>
-      <c r="T16" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="U16" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="V16" t="n" s="15">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="2:21" ht="66.0" customHeight="1">
-      <c r="B17" s="15">
-        <v>2003</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17" t="str" s="16">
-        <v>单位图标_临时英雄_3</v>
-      </c>
-      <c r="H17" t="str" s="16">
-        <v>单位立绘_临时英雄_3</v>
-      </c>
-      <c r="I17" t="str" s="16">
-        <v>$Lang$临时英雄_3_说明</v>
-      </c>
-      <c r="J17" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17"/>
-      <c r="L17"/>
-      <c r="M17" s="15" t="str">
-        <v>临时英雄普攻</v>
-      </c>
-      <c r="N17" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="O17" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="P17" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="R17" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="S17" s="10"/>
-      <c r="T17" s="13"/>
-      <c r="U17" s="6"/>
-    </row>
-    <row r="18" spans="2:21" ht="66.0" customHeight="1">
-      <c r="B18" s="15">
-        <v>2004</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="G18" t="str" s="16">
-        <v>单位图标_临时英雄_4</v>
-      </c>
-      <c r="H18" t="str" s="16">
-        <v>单位立绘_临时英雄_4</v>
-      </c>
-      <c r="I18" t="str" s="16">
-        <v>$Lang$临时英雄_4_说明</v>
-      </c>
-      <c r="J18" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18"/>
-      <c r="L18"/>
-      <c r="M18" s="15" t="str">
-        <v>临时英雄普攻</v>
-      </c>
-      <c r="N18" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="O18" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="P18" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="R18" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="S18" s="10"/>
-      <c r="T18" s="13"/>
-      <c r="U18" s="6"/>
+      <c r="V42" s="12"/>
+      <c r="W42" s="17"/>
+      <c r="X42" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2631,46 +4483,46 @@
     </row>
     <row r="3" s="2" customFormat="1" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>109</v>
+        <v>156</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:3">
       <c r="A5" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:3">
       <c r="A6" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2678,7 +4530,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2686,7 +4538,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2713,7 +4565,7 @@
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3" t="s">
-        <v>110</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:4">
@@ -2723,58 +4575,58 @@
     </row>
     <row r="3" s="2" customFormat="1" spans="1:4">
       <c r="A3" s="4" t="s">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>112</v>
+        <v>159</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>113</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>114</v>
+        <v>161</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:4">
@@ -2782,10 +4634,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>115</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:4">
@@ -2793,10 +4645,10 @@
         <v>2</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2804,10 +4656,10 @@
         <v>3</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2815,10 +4667,10 @@
         <v>4</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
